--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_C.B. JORGE JUAN CASTELLÓ SINCE 1907.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_C.B. JORGE JUAN CASTELLÓ SINCE 1907.xlsx
@@ -565,13 +565,13 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>19.6758</v>
+        <v>24.1812</v>
       </c>
       <c r="E2" t="n">
-        <v>11.4146</v>
+        <v>15.8982</v>
       </c>
       <c r="F2" t="n">
-        <v>8.261200000000001</v>
+        <v>8.282999999999999</v>
       </c>
       <c r="G2" t="n">
         <v>6.7396</v>
@@ -610,13 +610,13 @@
         <v>14.7186</v>
       </c>
       <c r="S2" t="n">
-        <v>-4.6005</v>
+        <v>-0.09499999999999981</v>
       </c>
       <c r="T2" t="n">
-        <v>-6.3926</v>
+        <v>-1.909</v>
       </c>
       <c r="U2" t="n">
-        <v>1.7922</v>
+        <v>1.814</v>
       </c>
       <c r="V2" t="n">
         <v>25.8395</v>
@@ -721,13 +721,13 @@
         <v>24</v>
       </c>
       <c r="D4" t="n">
-        <v>7.974799999999998</v>
+        <v>9.746099999999998</v>
       </c>
       <c r="E4" t="n">
-        <v>8.936499999999999</v>
+        <v>9.603300000000003</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.9617999999999998</v>
+        <v>0.1426000000000006</v>
       </c>
       <c r="G4" t="n">
         <v>18.3765</v>
@@ -766,13 +766,13 @@
         <v>45.6654</v>
       </c>
       <c r="S4" t="n">
-        <v>-4.933700000000001</v>
+        <v>-3.162700000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>-2.9744</v>
+        <v>-2.3075</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.9597</v>
+        <v>-0.8549000000000001</v>
       </c>
       <c r="V4" t="n">
         <v>-1.5052</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. PUJALTE MIRA</t>
+          <t>J. DE YRAOLAGOTIA TELLO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>23</v>
       </c>
       <c r="D5" t="n">
-        <v>5.124400000000001</v>
+        <v>2.768800000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>7.787100000000001</v>
+        <v>6.516400000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.6627</v>
+        <v>-3.7472</v>
       </c>
       <c r="G5" t="n">
-        <v>9.604900000000001</v>
+        <v>-4.065699999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.867599999999999</v>
+        <v>-1.4257</v>
       </c>
       <c r="I5" t="n">
-        <v>11.4724</v>
+        <v>-2.6401</v>
       </c>
       <c r="J5" t="n">
-        <v>33.0811</v>
+        <v>32.1809</v>
       </c>
       <c r="K5" t="n">
-        <v>16.9834</v>
+        <v>27.7079</v>
       </c>
       <c r="L5" t="n">
-        <v>16.0981</v>
+        <v>4.4726</v>
       </c>
       <c r="M5" t="n">
-        <v>-23.4763</v>
+        <v>-36.2466</v>
       </c>
       <c r="N5" t="n">
-        <v>-18.8505</v>
+        <v>-29.1337</v>
       </c>
       <c r="O5" t="n">
-        <v>-4.6255</v>
+        <v>-7.112399999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>1.887</v>
+        <v>13.7751</v>
       </c>
       <c r="Q5" t="n">
-        <v>-37.5513</v>
+        <v>-38.6835</v>
       </c>
       <c r="R5" t="n">
-        <v>39.4383</v>
+        <v>52.4586</v>
       </c>
       <c r="S5" t="n">
-        <v>3.5442</v>
+        <v>-5.2275</v>
       </c>
       <c r="T5" t="n">
-        <v>3.6924</v>
+        <v>-4.9225</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1483999999999999</v>
+        <v>-0.3048</v>
       </c>
       <c r="V5" t="n">
-        <v>-9.911300000000001</v>
+        <v>-1.7129</v>
       </c>
       <c r="W5" t="n">
-        <v>8.564400000000001</v>
+        <v>17.9414</v>
       </c>
       <c r="X5" t="n">
-        <v>-18.4758</v>
+        <v>-19.6543</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. DE YRAOLAGOTIA TELLO</t>
+          <t>I. NAVARRO SARMIENTO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>4.445399999999999</v>
+        <v>2.4701</v>
       </c>
       <c r="E6" t="n">
-        <v>6.1584</v>
+        <v>2.139</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.7131</v>
+        <v>0.3311</v>
       </c>
       <c r="G6" t="n">
-        <v>-4.065699999999999</v>
+        <v>1.9598</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.4257</v>
+        <v>2.4644</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.6401</v>
+        <v>-0.5047</v>
       </c>
       <c r="J6" t="n">
-        <v>32.1809</v>
+        <v>1.5005</v>
       </c>
       <c r="K6" t="n">
-        <v>27.7079</v>
+        <v>2.0919</v>
       </c>
       <c r="L6" t="n">
-        <v>4.4726</v>
+        <v>-0.5914</v>
       </c>
       <c r="M6" t="n">
-        <v>-36.2466</v>
+        <v>0.4593</v>
       </c>
       <c r="N6" t="n">
-        <v>-29.1337</v>
+        <v>0.3726</v>
       </c>
       <c r="O6" t="n">
-        <v>-7.112399999999999</v>
+        <v>0.08669999999999994</v>
       </c>
       <c r="P6" t="n">
-        <v>13.7751</v>
+        <v>0.7548</v>
       </c>
       <c r="Q6" t="n">
-        <v>-38.6835</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>52.4586</v>
+        <v>0.7548</v>
       </c>
       <c r="S6" t="n">
-        <v>-3.551099999999999</v>
+        <v>1.0006</v>
       </c>
       <c r="T6" t="n">
-        <v>-5.2799</v>
+        <v>0.6384</v>
       </c>
       <c r="U6" t="n">
-        <v>1.7292</v>
+        <v>0.3622</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.7129</v>
+        <v>-1.2452</v>
       </c>
       <c r="W6" t="n">
-        <v>17.9414</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-19.6543</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. NAVARRO SARMIENTO</t>
+          <t>J. PUJALTE MIRA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,70 +952,70 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="D7" t="n">
-        <v>2.5675</v>
+        <v>1.6405</v>
       </c>
       <c r="E7" t="n">
-        <v>2.2364</v>
+        <v>4.6152</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3311000000000001</v>
+        <v>-2.9748</v>
       </c>
       <c r="G7" t="n">
-        <v>1.9598</v>
+        <v>9.604900000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>2.4644</v>
+        <v>-1.867599999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5047</v>
+        <v>11.4724</v>
       </c>
       <c r="J7" t="n">
-        <v>1.5005</v>
+        <v>33.0811</v>
       </c>
       <c r="K7" t="n">
-        <v>2.0919</v>
+        <v>16.9834</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5914</v>
+        <v>16.0981</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4593</v>
+        <v>-23.4763</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3726</v>
+        <v>-18.8505</v>
       </c>
       <c r="O7" t="n">
-        <v>0.08669999999999994</v>
+        <v>-4.6255</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7548</v>
+        <v>1.887</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-37.5513</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7548</v>
+        <v>39.4383</v>
       </c>
       <c r="S7" t="n">
-        <v>1.0981</v>
+        <v>0.06009999999999993</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7359</v>
+        <v>0.5209</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3622</v>
+        <v>-0.4608000000000005</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2452</v>
+        <v>-9.911300000000001</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>8.564400000000001</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2452</v>
+        <v>-18.4758</v>
       </c>
     </row>
     <row r="8">
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. BUHORSKYI</t>
+          <t>D. ALBEROLA PALOMAR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.6013</v>
+        <v>0.1044</v>
       </c>
       <c r="E9" t="n">
-        <v>8.4133</v>
+        <v>-0.0764</v>
       </c>
       <c r="F9" t="n">
-        <v>-6.8118</v>
+        <v>0.1808</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.8037</v>
+        <v>0.0897</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.2</v>
+        <v>-0.0814</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.6036</v>
+        <v>0.171</v>
       </c>
       <c r="J9" t="n">
-        <v>9.7965</v>
+        <v>0.0411</v>
       </c>
       <c r="K9" t="n">
-        <v>6.7526</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>3.0436</v>
+        <v>0.0411</v>
       </c>
       <c r="M9" t="n">
-        <v>-14.6</v>
+        <v>0.0485</v>
       </c>
       <c r="N9" t="n">
-        <v>-8.9527</v>
+        <v>-0.0814</v>
       </c>
       <c r="O9" t="n">
-        <v>-5.6473</v>
+        <v>0.1299</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.0757</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-20.3796</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>18.3039</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>15.7665</v>
+        <v>0.0147</v>
       </c>
       <c r="T9" t="n">
-        <v>11.2994</v>
+        <v>-0.1176</v>
       </c>
       <c r="U9" t="n">
-        <v>4.4672</v>
+        <v>0.1323</v>
       </c>
       <c r="V9" t="n">
-        <v>-7.2859</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>7.697</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-14.9829</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. LOPEZ RICO</t>
+          <t>D. MARTINEZ VERDU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2947000000000002</v>
+        <v>-0.9435</v>
       </c>
       <c r="E10" t="n">
-        <v>1.6447</v>
+        <v>-0.9435</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.35</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>-6.4469</v>
+        <v>0.2598</v>
       </c>
       <c r="H10" t="n">
-        <v>-7.593800000000001</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>1.1467</v>
+        <v>0.2598</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.915</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>-4.709099999999999</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1.7943</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.532</v>
+        <v>0.2598</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.8845</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6476000000000001</v>
+        <v>0.2598</v>
       </c>
       <c r="P10" t="n">
-        <v>4.340100000000001</v>
+        <v>-0.9435</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4.151400000000001</v>
+        <v>-0.9435</v>
       </c>
       <c r="R10" t="n">
-        <v>8.4915</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>4.8957</v>
+        <v>-0.2598</v>
       </c>
       <c r="T10" t="n">
-        <v>6.8431</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.9479</v>
+        <v>-0.2598</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.4938</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.8678</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-4.3616</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. ALBEROLA PALOMAR</t>
+          <t>M. LOPEZ RICO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D11" t="n">
-        <v>0.025</v>
+        <v>-3.0775</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.0764</v>
+        <v>-1.958599999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1014</v>
+        <v>-1.1188</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0897</v>
+        <v>-6.4469</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.0814</v>
+        <v>-7.593800000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.171</v>
+        <v>1.1467</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0411</v>
+        <v>-2.915</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>-4.709099999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0411</v>
+        <v>1.7943</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0485</v>
+        <v>-3.532</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0814</v>
+        <v>-2.8845</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1299</v>
+        <v>-0.6476000000000001</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>4.340100000000001</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-4.151400000000001</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>8.4915</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.06469999999999999</v>
+        <v>1.5229</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1176</v>
+        <v>3.2396</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0529</v>
+        <v>-1.7167</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-2.4938</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.8678</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-4.3616</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. MARTINEZ VERDU</t>
+          <t>F. SELLER BERNABE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,61 +1342,61 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.9435</v>
+        <v>-3.1931</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.9435</v>
+        <v>-3.6606</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>0.4678</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2598</v>
+        <v>-1.7452</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>-0.1345</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2598</v>
+        <v>-1.6106</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>-2.3069</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>-0.5227999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>-1.7842</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2598</v>
+        <v>0.5617000000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>0.3882</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2598</v>
+        <v>0.1735</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>-0.9435</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>0.9435</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2598</v>
+        <v>-1.4477</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>-0.4102</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2598</v>
+        <v>-1.0374</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.9261</v>
+        <v>-3.5099</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.7606</v>
+        <v>-1.3709</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.1655</v>
+        <v>-2.139</v>
       </c>
       <c r="G13" t="n">
         <v>-2.1448</v>
@@ -1468,13 +1468,13 @@
         <v>0.1887</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5361</v>
+        <v>-0.1199</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2939</v>
+        <v>0.0958</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2422</v>
+        <v>-0.2157</v>
       </c>
       <c r="V13" t="n">
         <v>-1.2452</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>F. SELLER BERNABE</t>
+          <t>V. BERENGUER DEL VALLE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D14" t="n">
-        <v>-4.4099</v>
+        <v>-5.242600000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.4015</v>
+        <v>0.09819999999999984</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.008599999999999941</v>
+        <v>-5.3405</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.7452</v>
+        <v>-5.3907</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.1345</v>
+        <v>-3.8548</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.6106</v>
+        <v>-1.5359</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.3069</v>
+        <v>5.3964</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.5227999999999999</v>
+        <v>4.1214</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.7842</v>
+        <v>1.2753</v>
       </c>
       <c r="M14" t="n">
-        <v>0.5617000000000001</v>
+        <v>-10.7873</v>
       </c>
       <c r="N14" t="n">
-        <v>0.3882</v>
+        <v>-7.9763</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1735</v>
+        <v>-2.8112</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>8.4915</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9435</v>
+        <v>-6.9819</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9435</v>
+        <v>15.4734</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.6646</v>
+        <v>-1.25</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.1511</v>
+        <v>0.4953</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.5136</v>
+        <v>-1.7453</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>-7.093</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.1882</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-8.2812</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>V. BERENGUER DEL VALLE</t>
+          <t>V. VICENT TORTOSA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D15" t="n">
-        <v>-9.299200000000001</v>
+        <v>-6.0145</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.3463</v>
+        <v>6.645</v>
       </c>
       <c r="F15" t="n">
-        <v>-7.952300000000001</v>
+        <v>-12.6598</v>
       </c>
       <c r="G15" t="n">
-        <v>-5.3907</v>
+        <v>22.1943</v>
       </c>
       <c r="H15" t="n">
-        <v>-3.8548</v>
+        <v>15.6402</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.5359</v>
+        <v>6.5543</v>
       </c>
       <c r="J15" t="n">
-        <v>5.3964</v>
+        <v>39.0568</v>
       </c>
       <c r="K15" t="n">
-        <v>4.1214</v>
+        <v>28.8515</v>
       </c>
       <c r="L15" t="n">
-        <v>1.2753</v>
+        <v>10.2054</v>
       </c>
       <c r="M15" t="n">
-        <v>-10.7873</v>
+        <v>-16.8624</v>
       </c>
       <c r="N15" t="n">
-        <v>-7.9763</v>
+        <v>-13.2115</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.8112</v>
+        <v>-3.6511</v>
       </c>
       <c r="P15" t="n">
-        <v>8.4915</v>
+        <v>-15.4734</v>
       </c>
       <c r="Q15" t="n">
-        <v>-6.9819</v>
+        <v>-52.0812</v>
       </c>
       <c r="R15" t="n">
-        <v>15.4734</v>
+        <v>36.6078</v>
       </c>
       <c r="S15" t="n">
-        <v>-5.3067</v>
+        <v>-5.1499</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9492999999999999</v>
+        <v>-1.383</v>
       </c>
       <c r="U15" t="n">
-        <v>-4.3574</v>
+        <v>-3.7667</v>
       </c>
       <c r="V15" t="n">
-        <v>-7.093</v>
+        <v>-7.5854</v>
       </c>
       <c r="W15" t="n">
-        <v>1.1882</v>
+        <v>21.0524</v>
       </c>
       <c r="X15" t="n">
-        <v>-8.2812</v>
+        <v>-28.6378</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. PEREZ DIEZ</t>
+          <t>D. BUHORSKYI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D16" t="n">
-        <v>-10.3105</v>
+        <v>-8.374599999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>-8.7805</v>
+        <v>-0.1005999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.53</v>
+        <v>-8.273999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>-5.0769</v>
+        <v>-4.8037</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.6875</v>
+        <v>-2.2</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.3895</v>
+        <v>-2.6036</v>
       </c>
       <c r="J16" t="n">
-        <v>-2.2166</v>
+        <v>9.7965</v>
       </c>
       <c r="K16" t="n">
-        <v>0.001499999999999869</v>
+        <v>6.7526</v>
       </c>
       <c r="L16" t="n">
-        <v>-2.218</v>
+        <v>3.0436</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.8604</v>
+        <v>-14.6</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.6888</v>
+        <v>-8.9527</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1715</v>
+        <v>-5.6473</v>
       </c>
       <c r="P16" t="n">
-        <v>2.6418</v>
+        <v>-2.0757</v>
       </c>
       <c r="Q16" t="n">
-        <v>-6.7932</v>
+        <v>-20.3796</v>
       </c>
       <c r="R16" t="n">
-        <v>9.435</v>
+        <v>18.3039</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1088</v>
+        <v>5.7907</v>
       </c>
       <c r="T16" t="n">
-        <v>0.871</v>
+        <v>2.7857</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.7622</v>
+        <v>3.0049</v>
       </c>
       <c r="V16" t="n">
-        <v>-7.984</v>
+        <v>-7.2859</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.6415999999999999</v>
+        <v>7.697</v>
       </c>
       <c r="X16" t="n">
-        <v>-7.3424</v>
+        <v>-14.9829</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. GARCIA RUIZ</t>
+          <t>M. PEREZ DIEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,76 +1732,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="D17" t="n">
-        <v>-15.9475</v>
+        <v>-10.545</v>
       </c>
       <c r="E17" t="n">
-        <v>-8.041399999999999</v>
+        <v>-9.089599999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>-7.906200000000001</v>
+        <v>-1.4554</v>
       </c>
       <c r="G17" t="n">
-        <v>-14.1582</v>
+        <v>-5.0769</v>
       </c>
       <c r="H17" t="n">
-        <v>-8.1442</v>
+        <v>-2.6875</v>
       </c>
       <c r="I17" t="n">
-        <v>-6.0141</v>
+        <v>-2.3895</v>
       </c>
       <c r="J17" t="n">
-        <v>6.391800000000001</v>
+        <v>-2.2166</v>
       </c>
       <c r="K17" t="n">
-        <v>9.988299999999999</v>
+        <v>0.001499999999999869</v>
       </c>
       <c r="L17" t="n">
-        <v>-3.5963</v>
+        <v>-2.218</v>
       </c>
       <c r="M17" t="n">
-        <v>-20.5499</v>
+        <v>-2.8604</v>
       </c>
       <c r="N17" t="n">
-        <v>-18.1324</v>
+        <v>-2.6888</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.417899999999999</v>
+        <v>-0.1715</v>
       </c>
       <c r="P17" t="n">
-        <v>10.1898</v>
+        <v>2.6418</v>
       </c>
       <c r="Q17" t="n">
-        <v>-21.5118</v>
+        <v>-6.7932</v>
       </c>
       <c r="R17" t="n">
-        <v>31.7016</v>
+        <v>9.435</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3400000000000004</v>
+        <v>-0.1256999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>-2.5243</v>
+        <v>0.5616</v>
       </c>
       <c r="U17" t="n">
-        <v>2.8643</v>
+        <v>-0.6875</v>
       </c>
       <c r="V17" t="n">
-        <v>-12.3185</v>
+        <v>-7.984</v>
       </c>
       <c r="W17" t="n">
-        <v>9.6028</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="X17" t="n">
-        <v>-21.9213</v>
+        <v>-7.3424</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>V. VICENT TORTOSA</t>
+          <t>J. GARCIA CORBI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,76 +1810,76 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D18" t="n">
-        <v>-17.0087</v>
+        <v>-15.5035</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.777899999999999</v>
+        <v>-12.2501</v>
       </c>
       <c r="F18" t="n">
-        <v>-15.2309</v>
+        <v>-3.2533</v>
       </c>
       <c r="G18" t="n">
-        <v>22.1943</v>
+        <v>-8.629300000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>15.6402</v>
+        <v>-16.397</v>
       </c>
       <c r="I18" t="n">
-        <v>6.5543</v>
+        <v>7.767499999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>39.0568</v>
+        <v>5.8379</v>
       </c>
       <c r="K18" t="n">
-        <v>28.8515</v>
+        <v>-3.7005</v>
       </c>
       <c r="L18" t="n">
-        <v>10.2054</v>
+        <v>9.5383</v>
       </c>
       <c r="M18" t="n">
-        <v>-16.8624</v>
+        <v>-14.4673</v>
       </c>
       <c r="N18" t="n">
-        <v>-13.2115</v>
+        <v>-12.6965</v>
       </c>
       <c r="O18" t="n">
-        <v>-3.6511</v>
+        <v>-1.7709</v>
       </c>
       <c r="P18" t="n">
-        <v>-15.4734</v>
+        <v>2.075700000000001</v>
       </c>
       <c r="Q18" t="n">
-        <v>-52.0812</v>
+        <v>-22.644</v>
       </c>
       <c r="R18" t="n">
-        <v>36.6078</v>
+        <v>24.7197</v>
       </c>
       <c r="S18" t="n">
-        <v>-16.1441</v>
+        <v>-2.6449</v>
       </c>
       <c r="T18" t="n">
-        <v>-9.8065</v>
+        <v>-1.2542</v>
       </c>
       <c r="U18" t="n">
-        <v>-6.338</v>
+        <v>-1.3906</v>
       </c>
       <c r="V18" t="n">
-        <v>-7.5854</v>
+        <v>-6.304500000000001</v>
       </c>
       <c r="W18" t="n">
-        <v>21.0524</v>
+        <v>5.8102</v>
       </c>
       <c r="X18" t="n">
-        <v>-28.6378</v>
+        <v>-12.1147</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. GARCIA CORBI</t>
+          <t>A. GARCIA RUIZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,70 +1888,70 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D19" t="n">
-        <v>-21.5881</v>
+        <v>-17.0613</v>
       </c>
       <c r="E19" t="n">
-        <v>-15.86</v>
+        <v>-7.316000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>-5.7282</v>
+        <v>-9.7454</v>
       </c>
       <c r="G19" t="n">
-        <v>-8.629300000000001</v>
+        <v>-14.1582</v>
       </c>
       <c r="H19" t="n">
-        <v>-16.397</v>
+        <v>-8.1442</v>
       </c>
       <c r="I19" t="n">
-        <v>7.767499999999999</v>
+        <v>-6.0141</v>
       </c>
       <c r="J19" t="n">
-        <v>5.8379</v>
+        <v>6.391800000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>-3.7005</v>
+        <v>9.988299999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>9.5383</v>
+        <v>-3.5963</v>
       </c>
       <c r="M19" t="n">
-        <v>-14.4673</v>
+        <v>-20.5499</v>
       </c>
       <c r="N19" t="n">
-        <v>-12.6965</v>
+        <v>-18.1324</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.7709</v>
+        <v>-2.417899999999999</v>
       </c>
       <c r="P19" t="n">
-        <v>2.075700000000001</v>
+        <v>10.1898</v>
       </c>
       <c r="Q19" t="n">
-        <v>-22.644</v>
+        <v>-21.5118</v>
       </c>
       <c r="R19" t="n">
-        <v>24.7197</v>
+        <v>31.7016</v>
       </c>
       <c r="S19" t="n">
-        <v>-8.729900000000001</v>
+        <v>-0.7740000000000002</v>
       </c>
       <c r="T19" t="n">
-        <v>-4.8643</v>
+        <v>-1.7988</v>
       </c>
       <c r="U19" t="n">
-        <v>-3.8656</v>
+        <v>1.0249</v>
       </c>
       <c r="V19" t="n">
-        <v>-6.304500000000001</v>
+        <v>-12.3185</v>
       </c>
       <c r="W19" t="n">
-        <v>5.8102</v>
+        <v>9.6028</v>
       </c>
       <c r="X19" t="n">
-        <v>-12.1147</v>
+        <v>-21.9213</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>19</v>
       </c>
       <c r="D20" t="n">
-        <v>-25.1283</v>
+        <v>-20.4266</v>
       </c>
       <c r="E20" t="n">
-        <v>-24.0503</v>
+        <v>-23.3264</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.0782</v>
+        <v>2.900299999999999</v>
       </c>
       <c r="G20" t="n">
         <v>-9.5162</v>
@@ -2014,13 +2014,13 @@
         <v>35.6643</v>
       </c>
       <c r="S20" t="n">
-        <v>-8.850899999999999</v>
+        <v>-4.1487</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7077000000000001</v>
+        <v>0.01620000000000011</v>
       </c>
       <c r="U20" t="n">
-        <v>-8.1431</v>
+        <v>-4.1649</v>
       </c>
       <c r="V20" t="n">
         <v>-7.5159</v>
@@ -2047,13 +2047,13 @@
         <v>20</v>
       </c>
       <c r="D21" t="n">
-        <v>-48.9305</v>
+        <v>-43.2361</v>
       </c>
       <c r="E21" t="n">
-        <v>-29.906</v>
+        <v>-27.2516</v>
       </c>
       <c r="F21" t="n">
-        <v>-19.0247</v>
+        <v>-15.9845</v>
       </c>
       <c r="G21" t="n">
         <v>-23.3856</v>
@@ -2092,13 +2092,13 @@
         <v>38.8722</v>
       </c>
       <c r="S21" t="n">
-        <v>-14.2909</v>
+        <v>-8.5966</v>
       </c>
       <c r="T21" t="n">
-        <v>-6.6234</v>
+        <v>-3.9695</v>
       </c>
       <c r="U21" t="n">
-        <v>-7.6678</v>
+        <v>-4.627299999999999</v>
       </c>
       <c r="V21" t="n">
         <v>0.2572000000000005</v>
@@ -2125,19 +2125,19 @@
         <v>24</v>
       </c>
       <c r="D22" t="n">
-        <v>-97.0283</v>
+        <v>-77.462</v>
       </c>
       <c r="E22" t="n">
-        <v>-31.37569999999999</v>
+        <v>-22.85129999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>-65.6529</v>
+        <v>-54.60969999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>-7.513399999999995</v>
+        <v>-7.513400000000003</v>
       </c>
       <c r="H22" t="n">
-        <v>-59.2417</v>
+        <v>-59.24169999999999</v>
       </c>
       <c r="I22" t="n">
         <v>51.7289</v>
@@ -2149,7 +2149,7 @@
         <v>130.4783</v>
       </c>
       <c r="L22" t="n">
-        <v>91.16770000000001</v>
+        <v>91.1677</v>
       </c>
       <c r="M22" t="n">
         <v>-229.1591</v>
@@ -2164,19 +2164,19 @@
         <v>2.830500000000002</v>
       </c>
       <c r="Q22" t="n">
-        <v>-370.7955</v>
+        <v>-370.7954999999999</v>
       </c>
       <c r="R22" t="n">
         <v>373.626</v>
       </c>
       <c r="S22" t="n">
-        <v>-44.2385</v>
+        <v>-24.6722</v>
       </c>
       <c r="T22" t="n">
-        <v>-18.302</v>
+        <v>-9.7776</v>
       </c>
       <c r="U22" t="n">
-        <v>-25.9377</v>
+        <v>-14.8941</v>
       </c>
       <c r="V22" t="n">
         <v>-48.1041</v>
